--- a/CLIENT/DATExx-Whiddon/UNITS/BD/1. Input/AN-ACC Model ASH 2410.xlsx
+++ b/CLIENT/DATExx-Whiddon/UNITS/BD/1. Input/AN-ACC Model ASH 2410.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centri001.sharepoint.com/sites/4.Production/Shared Documents/WFEffectiveness/4.1.1 AGED CARE/01 Christadelphian Aged Care/240715/FACILITIES/ASHB/1. Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\CentriNOTSYNC\ResidentialCare\CLIENT\DATExx-Whiddon\UNITS\BD\1. Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{43AF48B6-8B39-4E0D-B336-54B5F123E315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFC54FDE-6309-4741-91F1-C225E5644E4B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E24201F-42B2-4245-90A2-7B0A6BA87DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35670" yWindow="285" windowWidth="33405" windowHeight="20295" tabRatio="839" activeTab="1" xr2:uid="{2363204A-BB9E-49CC-B0E9-E601DBCA756D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="839" activeTab="1" xr2:uid="{2363204A-BB9E-49CC-B0E9-E601DBCA756D}"/>
   </bookViews>
   <sheets>
     <sheet name="Primary Inputs" sheetId="14" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <sheet name="AN-ACC Worksheet" sheetId="25" r:id="rId10"/>
     <sheet name="AN-ACC Lookup Tables" sheetId="3" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1365,15 +1365,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1434,14 +1427,21 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Calculation" xfId="3" builtinId="22"/>
@@ -1468,10 +1468,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1799,14 +1795,14 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="156" t="s">
+      <c r="B5" s="178" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="158"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="180"/>
     </row>
     <row r="7" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A7" s="38" t="s">
@@ -2050,12 +2046,12 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="180" t="s">
+      <c r="C7" s="182" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="180"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="182"/>
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
@@ -2986,12 +2982,12 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="180" t="s">
+      <c r="C33" s="182" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="180"/>
-      <c r="E33" s="180"/>
-      <c r="F33" s="180"/>
+      <c r="D33" s="182"/>
+      <c r="E33" s="182"/>
+      <c r="F33" s="182"/>
     </row>
     <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
@@ -3922,12 +3918,12 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C59" s="180" t="s">
+      <c r="C59" s="182" t="s">
         <v>116</v>
       </c>
-      <c r="D59" s="180"/>
-      <c r="E59" s="180"/>
-      <c r="F59" s="180"/>
+      <c r="D59" s="182"/>
+      <c r="E59" s="182"/>
+      <c r="F59" s="182"/>
     </row>
     <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
@@ -6006,62 +6002,62 @@
         <v>152</v>
       </c>
       <c r="B10" s="22"/>
-      <c r="C10" s="167" t="s">
+      <c r="C10" s="166" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="168"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="169"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="167"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="168"/>
       <c r="J10" s="21"/>
-      <c r="K10" s="173" t="s">
+      <c r="K10" s="172" t="s">
         <v>156</v>
       </c>
-      <c r="L10" s="174"/>
-      <c r="M10" s="174"/>
-      <c r="N10" s="174"/>
-      <c r="O10" s="174"/>
-      <c r="P10" s="174"/>
-      <c r="Q10" s="175"/>
+      <c r="L10" s="173"/>
+      <c r="M10" s="173"/>
+      <c r="N10" s="173"/>
+      <c r="O10" s="173"/>
+      <c r="P10" s="173"/>
+      <c r="Q10" s="174"/>
       <c r="R10" s="21"/>
-      <c r="S10" s="161" t="s">
+      <c r="S10" s="160" t="s">
         <v>157</v>
       </c>
-      <c r="T10" s="162"/>
-      <c r="U10" s="162"/>
-      <c r="V10" s="162"/>
-      <c r="W10" s="162"/>
-      <c r="X10" s="162"/>
-      <c r="Y10" s="163"/>
+      <c r="T10" s="161"/>
+      <c r="U10" s="161"/>
+      <c r="V10" s="161"/>
+      <c r="W10" s="161"/>
+      <c r="X10" s="161"/>
+      <c r="Y10" s="162"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="21"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="170"/>
-      <c r="D11" s="171"/>
-      <c r="E11" s="171"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="171"/>
-      <c r="H11" s="171"/>
-      <c r="I11" s="172"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="170"/>
+      <c r="E11" s="170"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="170"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="171"/>
       <c r="J11" s="21"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="177"/>
-      <c r="M11" s="177"/>
-      <c r="N11" s="177"/>
-      <c r="O11" s="177"/>
-      <c r="P11" s="177"/>
-      <c r="Q11" s="178"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="176"/>
+      <c r="M11" s="176"/>
+      <c r="N11" s="176"/>
+      <c r="O11" s="176"/>
+      <c r="P11" s="176"/>
+      <c r="Q11" s="177"/>
       <c r="R11" s="21"/>
-      <c r="S11" s="164"/>
-      <c r="T11" s="165"/>
-      <c r="U11" s="165"/>
-      <c r="V11" s="165"/>
-      <c r="W11" s="165"/>
-      <c r="X11" s="165"/>
-      <c r="Y11" s="166"/>
+      <c r="S11" s="163"/>
+      <c r="T11" s="164"/>
+      <c r="U11" s="164"/>
+      <c r="V11" s="164"/>
+      <c r="W11" s="164"/>
+      <c r="X11" s="164"/>
+      <c r="Y11" s="165"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="21"/>
@@ -6889,10 +6885,10 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="159" t="s">
+      <c r="A30" s="158" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="160"/>
+      <c r="B30" s="159"/>
       <c r="C30" s="105"/>
       <c r="D30" s="106"/>
       <c r="E30" s="106"/>
@@ -7094,7 +7090,7 @@
         <f>D7/60</f>
         <v>358.74299999999999</v>
       </c>
-      <c r="F7" s="182">
+      <c r="F7" s="157">
         <f>E7*7</f>
         <v>2511.201</v>
       </c>
@@ -7109,7 +7105,7 @@
         <f>H7/60</f>
         <v>73.259999999999991</v>
       </c>
-      <c r="J7" s="182">
+      <c r="J7" s="157">
         <f>I7*7</f>
         <v>512.81999999999994</v>
       </c>
@@ -7281,43 +7277,43 @@
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="181"/>
-      <c r="C18" s="181" t="s">
+      <c r="B18" s="156"/>
+      <c r="C18" s="156" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="181"/>
-      <c r="E18" s="181"/>
-      <c r="F18" s="181"/>
-      <c r="G18" s="181" t="s">
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="181"/>
-      <c r="C19" s="181">
+      <c r="B19" s="156"/>
+      <c r="C19" s="156">
         <v>205.14</v>
       </c>
-      <c r="D19" s="181"/>
-      <c r="E19" s="181"/>
-      <c r="F19" s="181"/>
-      <c r="G19" s="181">
+      <c r="D19" s="156"/>
+      <c r="E19" s="156"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="156">
         <v>40.71</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="181" t="s">
+      <c r="B20" s="156" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="182">
+      <c r="C20" s="157">
         <f>C7/C19</f>
         <v>1.0598615579604174</v>
       </c>
-      <c r="D20" s="181"/>
-      <c r="E20" s="181"/>
-      <c r="F20" s="181" t="s">
+      <c r="D20" s="156"/>
+      <c r="E20" s="156"/>
+      <c r="F20" s="156" t="s">
         <v>194</v>
       </c>
-      <c r="G20" s="182">
+      <c r="G20" s="157">
         <f>G7/G19</f>
         <v>1.0906411201179071</v>
       </c>
@@ -7462,7 +7458,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="179" t="s">
+      <c r="T9" s="181" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="26"/>
@@ -7554,7 +7550,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="179"/>
+      <c r="T10" s="181"/>
       <c r="U10" s="26"/>
       <c r="V10" s="27" t="s">
         <v>63</v>
@@ -8658,7 +8654,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="179" t="s">
+      <c r="T9" s="181" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="26"/>
@@ -8722,7 +8718,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="179"/>
+      <c r="T10" s="181"/>
       <c r="U10" s="26"/>
       <c r="V10" s="27" t="s">
         <v>63</v>
@@ -10653,11 +10649,8 @@
   <mergeCells count="1">
     <mergeCell ref="T9:T10"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A38:A57" xr:uid="{A9B07C9A-20CF-4866-8EA0-202B63D92E07}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B38:B57" xr:uid="{25324BC0-7544-41F2-9F81-43F9CA09E489}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A38:B57" xr:uid="{A9B07C9A-20CF-4866-8EA0-202B63D92E07}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -10768,7 +10761,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="179" t="s">
+      <c r="T9" s="181" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="26"/>
@@ -10832,7 +10825,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="179"/>
+      <c r="T10" s="181"/>
       <c r="U10" s="26"/>
       <c r="V10" s="27" t="s">
         <v>63</v>
@@ -13288,11 +13281,8 @@
   <mergeCells count="1">
     <mergeCell ref="T9:T10"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A48:A71" xr:uid="{61EF124E-17B5-4912-B472-2612F0D91FF1}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B48:B71" xr:uid="{0842CCFA-25E5-4441-A1FE-7DF29A24B6ED}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A48:B71" xr:uid="{61EF124E-17B5-4912-B472-2612F0D91FF1}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -13403,7 +13393,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="179" t="s">
+      <c r="T9" s="181" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="26"/>
@@ -13467,7 +13457,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="179"/>
+      <c r="T10" s="181"/>
       <c r="U10" s="26"/>
       <c r="V10" s="27" t="s">
         <v>63</v>
@@ -15719,11 +15709,8 @@
   <mergeCells count="1">
     <mergeCell ref="T9:T10"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A51:A71" xr:uid="{2373DE6F-A634-4F73-8A82-DC1A8D3E54EE}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B51:B71" xr:uid="{C1A300D1-1B5F-41AA-B12C-1E9BCBC59C3C}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A51:B71" xr:uid="{2373DE6F-A634-4F73-8A82-DC1A8D3E54EE}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -15834,7 +15821,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="179" t="s">
+      <c r="T9" s="181" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="26"/>
@@ -15898,7 +15885,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="179"/>
+      <c r="T10" s="181"/>
       <c r="U10" s="26"/>
       <c r="V10" s="27" t="s">
         <v>63</v>
@@ -18150,11 +18137,8 @@
   <mergeCells count="1">
     <mergeCell ref="T9:T10"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A31:A71" xr:uid="{F4644399-00C8-4F29-B3FC-699F0E7E69E9}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B31:B71" xr:uid="{1481831B-90D2-4AD9-A98B-3B6A6E6B9A79}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A31:B71" xr:uid="{F4644399-00C8-4F29-B3FC-699F0E7E69E9}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -18265,7 +18249,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="179" t="s">
+      <c r="T9" s="181" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="26"/>
@@ -18329,7 +18313,7 @@
         <v>62</v>
       </c>
       <c r="S10" s="27"/>
-      <c r="T10" s="179"/>
+      <c r="T10" s="181"/>
       <c r="U10" s="26"/>
       <c r="V10" s="27" t="s">
         <v>63</v>
@@ -20652,6 +20636,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82d1b6b-c0e6-44b0-99a2-d357b2d50896">
@@ -20660,15 +20653,6 @@
     <TaxCatchAll xmlns="3be0b85a-8471-4f10-b038-505fde09e598" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20873,6 +20857,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52F6516-D81D-4ADE-8F50-4C185ACC3B5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3DC4443-1E43-4DEB-B6AC-EB1F2C393051}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -20887,18 +20879,27 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="f574b478-68e4-495d-9b17-0f93d51a8ef7"/>
     <ds:schemaRef ds:uri="a6ef9c2c-1ad1-4c09-9d1c-8c71a768c11f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52F6516-D81D-4ADE-8F50-4C185ACC3B5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="f82d1b6b-c0e6-44b0-99a2-d357b2d50896"/>
+    <ds:schemaRef ds:uri="3be0b85a-8471-4f10-b038-505fde09e598"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB42B34A-10C5-4515-94B0-EAEE7E2269E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB42B34A-10C5-4515-94B0-EAEE7E2269E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f82d1b6b-c0e6-44b0-99a2-d357b2d50896"/>
+    <ds:schemaRef ds:uri="3be0b85a-8471-4f10-b038-505fde09e598"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>